--- a/Excel/DynamoDB+Cost+Template.xlsx
+++ b/Excel/DynamoDB+Cost+Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/irmit/Library/CloudStorage/WorkDocsDrive-Documents/Irmi/TFC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{209DC081-EF65-2943-AF29-71D16A8A3420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9180FB6-EE4A-D641-9FFE-748DFBBBEA27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38400" yWindow="500" windowWidth="38400" windowHeight="19560" activeTab="2" xr2:uid="{8F366F91-9D43-B54C-80F1-BE22DE501760}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19560" xr2:uid="{8F366F91-9D43-B54C-80F1-BE22DE501760}"/>
   </bookViews>
   <sheets>
     <sheet name="CostSheet" sheetId="5" r:id="rId1"/>
@@ -462,6 +462,7 @@
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">The sum of the percentage of eventual cosistancy, strong consistancy, and transaction reads </t>
         </r>
@@ -472,6 +473,7 @@
             <color rgb="FFFF0000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">must be equal to 100%. </t>
         </r>
@@ -481,6 +483,7 @@
             <color rgb="FFFF0000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -491,6 +494,7 @@
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>The default is 100% eventual consistency.</t>
         </r>
@@ -1181,7 +1185,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="212">
   <si>
     <t>Actual Storage</t>
   </si>
@@ -1725,6 +1729,114 @@
     <t>RatioOD_RCU</t>
   </si>
   <si>
+    <t>RCU</t>
+  </si>
+  <si>
+    <t>WCU</t>
+  </si>
+  <si>
+    <t>Storage</t>
+  </si>
+  <si>
+    <t>Unit size (KB) for reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On Demand price per each unit consumed </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provisioned hourly pricing for a level of 1 Unit per second </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Storage Costs per GB-hr </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time unit </t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time unit Qty </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provisioning Efficiency % </t>
+  </si>
+  <si>
+    <t>Global Table?</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> On Demand mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Provisioned mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Storage</t>
+  </si>
+  <si>
+    <t>Average read units per second</t>
+  </si>
+  <si>
+    <t>Read cost:</t>
+  </si>
+  <si>
+    <t>Average write units per second</t>
+  </si>
+  <si>
+    <t>Write cost:</t>
+  </si>
+  <si>
+    <t>Table size in GB</t>
+  </si>
+  <si>
+    <t>Storage cost:</t>
+  </si>
+  <si>
+    <t>Green values can be changed to adjust the cost model</t>
+  </si>
+  <si>
+    <t>DynamoDB capacity is either On Demand or Provisioned. This model shows you the cost of each, and assumes you would need to over provision somewhat, resulting in less than 100% provisioning efficiency.</t>
+  </si>
+  <si>
+    <t>**Note: Global Tables simplifies prices to 2x storage and 3x write costs compared to the single region table</t>
+  </si>
+  <si>
+    <t>Time Unit List</t>
+  </si>
+  <si>
+    <t>Global Tables</t>
+  </si>
+  <si>
+    <t>Hour</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>Yes, 2 regions</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Actual Read/Write Cost($):</t>
+  </si>
+  <si>
+    <t>Actual Storage Cost($):</t>
+  </si>
+  <si>
+    <t>TotalCost($):</t>
+  </si>
+  <si>
+    <t>Yes, 3 regions</t>
+  </si>
+  <si>
+    <t>Yes, MRSC</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">DynamoDB Cost Template
 </t>
@@ -1735,110 +1847,8 @@
         <color theme="0"/>
         <rFont val="Calibri (Body)"/>
       </rPr>
-      <t>Prices in us-east-1</t>
+      <t>Prices in us-east-1, updated for 2025</t>
     </r>
-  </si>
-  <si>
-    <t>RCU</t>
-  </si>
-  <si>
-    <t>WCU</t>
-  </si>
-  <si>
-    <t>Storage</t>
-  </si>
-  <si>
-    <t>Unit size (KB) for reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On Demand price per each unit consumed </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Provisioned hourly pricing for a level of 1 Unit per second </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Storage Costs per GB-hr </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time unit </t>
-  </si>
-  <si>
-    <t>Month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time unit Qty </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Provisioning Efficiency % </t>
-  </si>
-  <si>
-    <t>Global Table?</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> On Demand mode</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Provisioned mode</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Storage</t>
-  </si>
-  <si>
-    <t>Average read units per second</t>
-  </si>
-  <si>
-    <t>Read cost:</t>
-  </si>
-  <si>
-    <t>Average write units per second</t>
-  </si>
-  <si>
-    <t>Write cost:</t>
-  </si>
-  <si>
-    <t>Table size in GB</t>
-  </si>
-  <si>
-    <t>Storage cost:</t>
-  </si>
-  <si>
-    <t>Green values can be changed to adjust the cost model</t>
-  </si>
-  <si>
-    <t>DynamoDB capacity is either On Demand or Provisioned. This model shows you the cost of each, and assumes you would need to over provision somewhat, resulting in less than 100% provisioning efficiency.</t>
-  </si>
-  <si>
-    <t>**Note: Global Tables simplifies prices to 2x storage and 3x write costs compared to the single region table</t>
-  </si>
-  <si>
-    <t>Time Unit List</t>
-  </si>
-  <si>
-    <t>Global Tables</t>
-  </si>
-  <si>
-    <t>Hour</t>
-  </si>
-  <si>
-    <t>Day</t>
-  </si>
-  <si>
-    <t>Yes, 2 regions</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>Actual Read/Write Cost($):</t>
-  </si>
-  <si>
-    <t>Actual Storage Cost($):</t>
-  </si>
-  <si>
-    <t>TotalCost($):</t>
   </si>
 </sst>
 </file>
@@ -2135,6 +2145,21 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -2250,19 +2275,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -3633,56 +3645,56 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="171" fontId="49" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="51" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="172" fontId="49" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="172" fontId="51" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="173" fontId="49" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="51" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="49" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="51" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="51" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="53" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="51" fillId="5" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="53" fillId="5" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="51" fillId="5" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="53" fillId="5" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="2" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="2" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -3697,22 +3709,22 @@
     <xf numFmtId="2" fontId="12" fillId="5" borderId="88" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="51" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="53" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="51" fillId="5" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="53" fillId="5" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="51" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="53" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3862,10 +3874,10 @@
     <xf numFmtId="164" fontId="14" fillId="6" borderId="64" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="2" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="2" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="2" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="2" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="3" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3877,10 +3889,10 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="2" borderId="89" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="2" borderId="89" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="2" borderId="90" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="2" borderId="90" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="3" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3895,10 +3907,10 @@
     <xf numFmtId="166" fontId="4" fillId="3" borderId="91" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="2" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="2" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="2" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="2" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="3" borderId="82" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3913,10 +3925,10 @@
     <xf numFmtId="166" fontId="4" fillId="3" borderId="86" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4224,6 +4236,306 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="169" formatCode="0.00000"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF333333"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="170" formatCode="0.0000"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF333333"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="170" formatCode="0.0000"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF333333"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="170" formatCode="0.0000"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF333333"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="170" formatCode="0.0000"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF333333"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="170" formatCode="0.0000"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF333333"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="170" formatCode="0.0000"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF333333"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="170" formatCode="0.0000"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF333333"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="170" formatCode="0.0000"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF333333"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="168" formatCode="0.0000000"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF333333"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="168" formatCode="0.0000000"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF333333"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="168" formatCode="0.0000000"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF333333"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="168" formatCode="0.0000000"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF333333"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="169" formatCode="0.00000"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF333333"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="169" formatCode="0.00000"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF333333"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="170" formatCode="0.0000"/>
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -4556,306 +4868,6 @@
           <bgColor rgb="FFBFBFBF"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color rgb="FF333333"/>
-        <name val="Helvetica Neue"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="170" formatCode="0.0000"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color rgb="FF333333"/>
-        <name val="Helvetica Neue"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="170" formatCode="0.0000"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color rgb="FF333333"/>
-        <name val="Helvetica Neue"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="170" formatCode="0.0000"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color rgb="FF333333"/>
-        <name val="Helvetica Neue"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="170" formatCode="0.0000"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color rgb="FF333333"/>
-        <name val="Helvetica Neue"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="170" formatCode="0.0000"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color rgb="FF333333"/>
-        <name val="Helvetica Neue"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="170" formatCode="0.0000"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color rgb="FF333333"/>
-        <name val="Helvetica Neue"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="170" formatCode="0.0000"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color rgb="FF333333"/>
-        <name val="Helvetica Neue"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="170" formatCode="0.0000"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color rgb="FF333333"/>
-        <name val="Helvetica Neue"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="170" formatCode="0.0000"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color rgb="FF333333"/>
-        <name val="Helvetica Neue"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="168" formatCode="0.0000000"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color rgb="FF333333"/>
-        <name val="Helvetica Neue"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="168" formatCode="0.0000000"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color rgb="FF333333"/>
-        <name val="Helvetica Neue"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="168" formatCode="0.0000000"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color rgb="FF333333"/>
-        <name val="Helvetica Neue"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="168" formatCode="0.0000000"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color rgb="FF333333"/>
-        <name val="Helvetica Neue"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="169" formatCode="0.00000"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color rgb="FF333333"/>
-        <name val="Helvetica Neue"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="169" formatCode="0.00000"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -6279,37 +6291,37 @@
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{D6EA7312-83FB-3648-A8CB-C88F5565BFA1}" name="Table4" displayName="Table4" ref="A2:S34" totalsRowCount="1">
   <autoFilter ref="A2:S33" xr:uid="{D6EA7312-83FB-3648-A8CB-C88F5565BFA1}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:S33">
-    <sortCondition ref="D2:D33"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:N33">
+    <sortCondition descending="1" ref="A2:A33"/>
   </sortState>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{4F795EE2-B6FB-B742-8C31-9011902642B6}" name="# aws_region"/>
     <tableColumn id="2" xr3:uid="{CF4D784D-46E9-0C4C-81E2-62740353765A}" name="country_code"/>
     <tableColumn id="3" xr3:uid="{D47278EA-DC28-EA4F-9DFB-6558884EA6FA}" name="region_code"/>
     <tableColumn id="4" xr3:uid="{47C66DF7-3845-274F-9EA1-D5156FF306E8}" name="city"/>
-    <tableColumn id="6" xr3:uid="{4CA20C9C-C0C9-404C-A063-3757A6C99919}" name="Standard" dataDxfId="61" totalsRowDxfId="14"/>
-    <tableColumn id="15" xr3:uid="{3041EACD-1693-EC4F-9928-6C3936D206CE}" name="Standard_IA" dataDxfId="60" totalsRowDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{EC65115E-728D-C840-BE66-3C6FD170968F}" name="Provisioned - WCU" dataDxfId="59" totalsRowDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{E5D67E0F-AD04-A149-93D6-A3AF2ECE2F41}" name="Provisioned - RCU" dataDxfId="58" totalsRowDxfId="11"/>
-    <tableColumn id="10" xr3:uid="{63500D62-826A-BE41-A0E4-E4BC0A60313C}" name="Provisioned_IA- WCU" dataDxfId="57" totalsRowDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{8B367489-BF7E-8B4F-9611-FA953AD6C79E}" name="Provisioned_IA- RCU" dataDxfId="56" totalsRowDxfId="9"/>
-    <tableColumn id="12" xr3:uid="{DF393429-B26C-0046-A59F-F50B43491C0C}" name="OD_WRU" dataDxfId="55" totalsRowDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{772E548A-0178-ED47-9354-38D5057D5EBD}" name="OD_RRU" dataDxfId="54" totalsRowDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{8B38EE2D-1D3C-9F4A-9EB7-08BD8A62CE3A}" name="OD_IA_WRU" dataDxfId="53" totalsRowDxfId="6"/>
-    <tableColumn id="13" xr3:uid="{FBA18991-3DBC-224E-B3CB-E81BC4ACEFC0}" name="OD_IA_RRU" dataDxfId="52" totalsRowDxfId="5"/>
-    <tableColumn id="17" xr3:uid="{E61725AA-8D5A-0242-B068-AFECA7F4B791}" name="Ratio_P_WCU" dataDxfId="51" totalsRowDxfId="4">
+    <tableColumn id="6" xr3:uid="{4CA20C9C-C0C9-404C-A063-3757A6C99919}" name="Standard" dataDxfId="28" totalsRowDxfId="14"/>
+    <tableColumn id="15" xr3:uid="{3041EACD-1693-EC4F-9928-6C3936D206CE}" name="Standard_IA" dataDxfId="27" totalsRowDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{EC65115E-728D-C840-BE66-3C6FD170968F}" name="Provisioned - WCU" dataDxfId="26" totalsRowDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{E5D67E0F-AD04-A149-93D6-A3AF2ECE2F41}" name="Provisioned - RCU" dataDxfId="25" totalsRowDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{63500D62-826A-BE41-A0E4-E4BC0A60313C}" name="Provisioned_IA- WCU" dataDxfId="24" totalsRowDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{8B367489-BF7E-8B4F-9611-FA953AD6C79E}" name="Provisioned_IA- RCU" dataDxfId="23" totalsRowDxfId="9"/>
+    <tableColumn id="12" xr3:uid="{DF393429-B26C-0046-A59F-F50B43491C0C}" name="OD_WRU" dataDxfId="21" totalsRowDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{772E548A-0178-ED47-9354-38D5057D5EBD}" name="OD_RRU" dataDxfId="20" totalsRowDxfId="7"/>
+    <tableColumn id="11" xr3:uid="{8B38EE2D-1D3C-9F4A-9EB7-08BD8A62CE3A}" name="OD_IA_WRU" dataDxfId="19" totalsRowDxfId="6"/>
+    <tableColumn id="13" xr3:uid="{FBA18991-3DBC-224E-B3CB-E81BC4ACEFC0}" name="OD_IA_RRU" dataDxfId="18" totalsRowDxfId="5"/>
+    <tableColumn id="17" xr3:uid="{E61725AA-8D5A-0242-B068-AFECA7F4B791}" name="Ratio_P_WCU" dataDxfId="17" totalsRowDxfId="4">
       <calculatedColumnFormula>Table4[[#This Row],[Provisioned_IA- WCU]]/Table4[[#This Row],[Provisioned - WCU]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{2B5D4F38-E0AF-9E43-8E63-3D8CCA639A89}" name="Ratio_P_RCU" dataDxfId="50" totalsRowDxfId="3">
+    <tableColumn id="18" xr3:uid="{2B5D4F38-E0AF-9E43-8E63-3D8CCA639A89}" name="Ratio_P_RCU" dataDxfId="16" totalsRowDxfId="3">
       <calculatedColumnFormula>Table4[[#This Row],[Provisioned_IA- RCU]]/Table4[[#This Row],[Provisioned - RCU]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{44B28A4F-B169-BA49-A308-438B27B979B0}" name="RationOD_WCU" dataDxfId="49" totalsRowDxfId="2">
+    <tableColumn id="19" xr3:uid="{44B28A4F-B169-BA49-A308-438B27B979B0}" name="RationOD_WCU" dataDxfId="15" totalsRowDxfId="2">
       <calculatedColumnFormula>Table4[[#This Row],[OD_IA_WRU]]/Table4[[#This Row],[OD_WRU]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{401D964D-329D-F747-A4C3-8903B6AEB0CB}" name="RatioOD_RCU" dataDxfId="48" totalsRowDxfId="1">
+    <tableColumn id="20" xr3:uid="{401D964D-329D-F747-A4C3-8903B6AEB0CB}" name="RatioOD_RCU" dataDxfId="29" totalsRowDxfId="1">
       <calculatedColumnFormula>Table4[[#This Row],[OD_IA_RRU]]/Table4[[#This Row],[OD_RRU]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{17D9228B-9461-7A44-879C-1782D7D904B9}" name="RatioStorage" dataDxfId="47" totalsRowDxfId="0">
+    <tableColumn id="21" xr3:uid="{17D9228B-9461-7A44-879C-1782D7D904B9}" name="RatioStorage" dataDxfId="22" totalsRowDxfId="0">
       <calculatedColumnFormula>Table4[[#This Row],[Standard_IA]]/Table4[[#This Row],[Standard]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6614,11 +6626,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74A5111F-7B7D-344C-A811-3E0902529217}">
-  <dimension ref="B1:G34"/>
+  <dimension ref="B1:G31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="42.5" customWidth="1"/>
+    <col min="1" max="1" width="1.83203125" customWidth="1"/>
+    <col min="2" max="2" width="45.33203125" customWidth="1"/>
     <col min="3" max="3" width="17.1640625" customWidth="1"/>
     <col min="4" max="4" width="14.5" customWidth="1"/>
     <col min="5" max="5" width="17.5" customWidth="1"/>
@@ -6629,21 +6641,21 @@
     <row r="1" spans="2:7" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:7" s="84" customFormat="1" ht="38" x14ac:dyDescent="0.2">
       <c r="B2" s="81" t="s">
+        <v>211</v>
+      </c>
+      <c r="C2" s="82" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="82" t="s">
+      <c r="D2" s="82" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="82" t="s">
+      <c r="E2" s="83" t="s">
         <v>177</v>
-      </c>
-      <c r="E2" s="83" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="19" x14ac:dyDescent="0.25">
       <c r="B3" s="85" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C3" s="86">
         <v>4</v>
@@ -6655,21 +6667,21 @@
     </row>
     <row r="4" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="85" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C4" s="88">
-        <f>0.25/1000000</f>
-        <v>2.4999999999999999E-7</v>
+        <f>0.125/1000000</f>
+        <v>1.2499999999999999E-7</v>
       </c>
       <c r="D4" s="88">
-        <f>1.25/1000000</f>
-        <v>1.2500000000000001E-6</v>
+        <f>0.625/1000000</f>
+        <v>6.2500000000000005E-7</v>
       </c>
       <c r="E4" s="87"/>
     </row>
     <row r="5" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="85" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C5" s="89">
         <v>1.2999999999999999E-4</v>
@@ -6684,7 +6696,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B7" s="85" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C7" s="90"/>
       <c r="D7" s="90"/>
@@ -6694,15 +6706,15 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B9" s="92" t="s">
+        <v>182</v>
+      </c>
+      <c r="C9" s="93" t="s">
         <v>183</v>
-      </c>
-      <c r="C9" s="93" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="92" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C10" s="93">
         <v>1</v>
@@ -6714,7 +6726,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B11" s="92" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C11" s="95">
         <v>50</v>
@@ -6722,17 +6734,17 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="92" t="s">
+        <v>186</v>
+      </c>
+      <c r="C12" s="93" t="s">
         <v>187</v>
       </c>
-      <c r="C12" s="93" t="s">
-        <v>188</v>
-      </c>
       <c r="E12" s="94">
-        <f>_xlfn.SWITCH(GT, "No", 1, "Yes, 2 regions", 2)</f>
+        <f>_xlfn.SWITCH(GT, "No", 1, "Yes, 2 regions", 2, "Yes, 3 regions", 3, "Yes, MRSC", 3)</f>
         <v>1</v>
       </c>
       <c r="F12" s="94">
-        <f>_xlfn.SWITCH(GT, "No", 1, "Yes, 2 regions", 3)</f>
+        <f>_xlfn.SWITCH(GT, "No", 1, "Yes, 2 regions", 2, "Yes, 3 regions", 3, "Yes, MRSC", 3)</f>
         <v>1</v>
       </c>
     </row>
@@ -6747,28 +6759,28 @@
     </row>
     <row r="15" spans="2:7" s="96" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="E15" s="99" t="s">
+        <v>188</v>
+      </c>
+      <c r="F15" s="100" t="s">
         <v>189</v>
       </c>
-      <c r="F15" s="100" t="s">
+      <c r="G15" s="101" t="s">
         <v>190</v>
-      </c>
-      <c r="G15" s="101" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="21" x14ac:dyDescent="0.25">
       <c r="B16" s="102" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C16" s="103">
         <v>100</v>
       </c>
       <c r="D16" s="104" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E16" s="105">
         <f>C16*OnDemandRcuPrice*3600*Hours</f>
-        <v>64.8</v>
+        <v>32.4</v>
       </c>
       <c r="F16" s="106">
         <f>C16*ProvisionedPricePerReadUnitHourly*Hours*(1/(ProvisioningEfficiency/100))</f>
@@ -6778,17 +6790,17 @@
     </row>
     <row r="17" spans="2:7" ht="21" x14ac:dyDescent="0.25">
       <c r="B17" s="102" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C17" s="103">
         <v>100</v>
       </c>
       <c r="D17" s="104" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E17" s="108">
         <f>C17*OnDemandWcuPrice*3600*Hours*GTWrites</f>
-        <v>324</v>
+        <v>162</v>
       </c>
       <c r="F17" s="109">
         <f>C17*ProvisionedPricePerWriteUnitHourly*Hours*(1/(ProvisioningEfficiency/100))*GTWrites</f>
@@ -6798,13 +6810,13 @@
     </row>
     <row r="18" spans="2:7" ht="21" x14ac:dyDescent="0.25">
       <c r="B18" s="102" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C18" s="103">
         <v>100</v>
       </c>
       <c r="D18" s="104" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E18" s="107"/>
       <c r="F18" s="107"/>
@@ -6815,69 +6827,71 @@
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B22" s="110" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="110" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B24" s="110" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" hidden="1" x14ac:dyDescent="0.2"/>
+        <v>199</v>
+      </c>
+    </row>
     <row r="26" spans="2:7" hidden="1" x14ac:dyDescent="0.2"/>
     <row r="27" spans="2:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
+        <v>200</v>
+      </c>
+      <c r="C27" t="s">
         <v>201</v>
-      </c>
-      <c r="C27" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="28" spans="2:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C28" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="29" spans="2:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
+        <v>203</v>
+      </c>
+      <c r="C29" t="s">
         <v>204</v>
-      </c>
-      <c r="C29" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="30" spans="2:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
-        <v>184</v>
+        <v>183</v>
+      </c>
+      <c r="C30" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="31" spans="2:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="33" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="34" hidden="1" x14ac:dyDescent="0.2"/>
+        <v>205</v>
+      </c>
+      <c r="C31" t="s">
+        <v>210</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C12" xr:uid="{EA6DDBB6-4213-C942-AEE9-964048E9D090}">
-      <formula1>$C$28:$C$29</formula1>
-    </dataValidation>
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C11" xr:uid="{D6E42FBD-5461-444E-81E0-C34F8E03CE7D}">
       <formula1>1</formula1>
       <formula2>100</formula2>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C9" xr:uid="{002149AF-C7EA-E945-B9C4-26D82F61BFEA}">
       <formula1>$B$28:$B$31</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C12" xr:uid="{EA6DDBB6-4213-C942-AEE9-964048E9D090}">
+      <formula1>$C$28:$C$31</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7004,11 +7018,11 @@
         <v>131</v>
       </c>
       <c r="H6" s="56">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="I6" s="59" t="str">
         <f>H6*1024&amp;(" Bytes")</f>
-        <v>1474.56 Bytes</v>
+        <v>2048 Bytes</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="22" thickBot="1" x14ac:dyDescent="0.3">
@@ -7151,7 +7165,7 @@
         <v>130</v>
       </c>
       <c r="H13" s="56">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I13" s="59"/>
     </row>
@@ -7224,7 +7238,7 @@
       </c>
       <c r="L16" s="160">
         <f>$K$16+$K$18</f>
-        <v>182.19</v>
+        <v>160.965</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="30" thickBot="1" x14ac:dyDescent="0.4">
@@ -7277,13 +7291,13 @@
       </c>
       <c r="H18" s="155">
         <f>IF($H$13&gt;25,$H$13*$O$30-25*$O$30,0)</f>
-        <v>21.224999999999998</v>
+        <v>0</v>
       </c>
       <c r="I18" s="156"/>
       <c r="J18" s="157"/>
       <c r="K18" s="45">
         <f>IF($H$13&gt;25,$H$13*$O$30-25*$O$30,0)</f>
-        <v>21.224999999999998</v>
+        <v>0</v>
       </c>
       <c r="L18" s="162"/>
     </row>
@@ -7383,7 +7397,7 @@
       </c>
       <c r="L21" s="163">
         <f>$K$21+$K$23</f>
-        <v>209.76142857142858</v>
+        <v>201.27142857142857</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="29" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7418,13 +7432,13 @@
       </c>
       <c r="H23" s="158">
         <f>IF($H$13&gt;25,$H$13*$P$30-25*$P$30,0)</f>
-        <v>8.49</v>
+        <v>0</v>
       </c>
       <c r="I23" s="156"/>
       <c r="J23" s="157"/>
       <c r="K23" s="45">
         <f>IF($H$13&gt;25,$H$13*$P$30-25*$P$30,0)</f>
-        <v>8.49</v>
+        <v>0</v>
       </c>
       <c r="L23" s="165"/>
     </row>
@@ -7448,7 +7462,7 @@
       </c>
       <c r="H26" s="54" cm="1">
         <f t="array" ref="H26">_xlfn.IFS($G$26="Candidate to Standard",$L$21-$L$16,$G$26="Candidate to Standard-IA",$L$16-$L$21,$G$26="Even", 0)</f>
-        <v>27.571428571428584</v>
+        <v>40.306428571428569</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -7510,19 +7524,19 @@
       </c>
       <c r="K30" s="33">
         <f>VLOOKUP($H$5,Table4[#All],11,0)</f>
-        <v>0.70499999999999996</v>
+        <v>0.75</v>
       </c>
       <c r="L30" s="33">
         <f>VLOOKUP($H$5,Table4[#All],12,0)</f>
-        <v>0.14149999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="M30" s="33">
         <f>VLOOKUP($H$5,Table4[#All],13,0)</f>
-        <v>0.88500000000000001</v>
+        <v>0.9375</v>
       </c>
       <c r="N30" s="33">
         <f>VLOOKUP($H$5,Table4[#All],14,0)</f>
-        <v>0.17699999999999999</v>
+        <v>0.1875</v>
       </c>
       <c r="O30" s="30">
         <f>VLOOKUP($H$5,Table4[#All],5,0)</f>
@@ -7546,11 +7560,11 @@
       </c>
       <c r="M35">
         <f>$M$30/$K$30</f>
-        <v>1.2553191489361704</v>
+        <v>1.25</v>
       </c>
       <c r="N35">
         <f>$N$30/$L$30</f>
-        <v>1.2508833922261484</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="36" spans="8:16" hidden="1" x14ac:dyDescent="0.2">
@@ -7567,7 +7581,7 @@
       </c>
       <c r="M36" s="159">
         <f>$N$35*($H$11/($H$11+$H$12))+$M$35*($H$12/($H$12+$H$11))</f>
-        <v>1.2531012705811593</v>
+        <v>1.25</v>
       </c>
       <c r="N36" s="159"/>
       <c r="P36">
@@ -7609,72 +7623,72 @@
     <mergeCell ref="B7:C7"/>
   </mergeCells>
   <conditionalFormatting sqref="A9">
-    <cfRule type="cellIs" dxfId="46" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="61" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>0.4166</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="60" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>41.66%</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="59" priority="13" operator="greaterThan">
       <formula>0.1333</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="14" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="58" priority="14" operator="lessThanOrEqual">
       <formula>13.33%</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21">
-    <cfRule type="cellIs" dxfId="42" priority="15" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="57" priority="15" operator="greaterThan">
       <formula>0.1333</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="16" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="56" priority="16" operator="lessThanOrEqual">
       <formula>13.33%</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9">
-    <cfRule type="containsText" dxfId="40" priority="9" operator="containsText" text="Candidate">
+    <cfRule type="containsText" dxfId="55" priority="9" operator="containsText" text="Candidate">
       <formula>NOT(ISERROR(SEARCH("Candidate",D9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="39" priority="10" stopIfTrue="1" operator="containsText" text="Optimized">
+    <cfRule type="containsText" dxfId="54" priority="10" stopIfTrue="1" operator="containsText" text="Optimized">
       <formula>NOT(ISERROR(SEARCH("Optimized",D9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D21">
-    <cfRule type="containsText" dxfId="38" priority="7" operator="containsText" text="Optimized">
+    <cfRule type="containsText" dxfId="53" priority="7" operator="containsText" text="Optimized">
       <formula>NOT(ISERROR(SEARCH("Optimized",D21)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="37" priority="8" operator="containsText" text="Candidate">
+    <cfRule type="containsText" dxfId="52" priority="8" operator="containsText" text="Candidate">
       <formula>NOT(ISERROR(SEARCH("Candidate",D21)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="cellIs" dxfId="36" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="51" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="50" priority="6" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21">
-    <cfRule type="cellIs" dxfId="34" priority="17" operator="lessThan">
+    <cfRule type="cellIs" dxfId="49" priority="17" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="18" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="48" priority="18" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G26">
-    <cfRule type="containsText" dxfId="32" priority="1" operator="containsText" text="Candidate">
+    <cfRule type="containsText" dxfId="47" priority="1" operator="containsText" text="Candidate">
       <formula>NOT(ISERROR(SEARCH("Candidate",G26)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="31" priority="2" stopIfTrue="1" operator="containsText" text="Optimized">
+    <cfRule type="containsText" dxfId="46" priority="2" stopIfTrue="1" operator="containsText" text="Optimized">
       <formula>NOT(ISERROR(SEARCH("Optimized",G26)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26">
-    <cfRule type="cellIs" dxfId="30" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="45" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="44" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7750,7 +7764,7 @@
     </row>
     <row r="5" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B5" s="168">
         <v>1000</v>
@@ -7764,7 +7778,7 @@
     </row>
     <row r="6" spans="1:6" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B6" s="179">
         <v>100</v>
@@ -7778,7 +7792,7 @@
     </row>
     <row r="7" spans="1:6" ht="22" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B7" s="176">
         <f>SUM(B5:B6)</f>
@@ -8008,56 +8022,56 @@
     <mergeCell ref="D4:E4"/>
   </mergeCells>
   <conditionalFormatting sqref="A9">
-    <cfRule type="cellIs" dxfId="28" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="43" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>0.4166</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="42" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>41.66%</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="41" priority="13" operator="greaterThan">
       <formula>0.1333</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="14" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="40" priority="14" operator="lessThanOrEqual">
       <formula>13.33%</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21">
-    <cfRule type="cellIs" dxfId="24" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="39" priority="3" operator="greaterThan">
       <formula>0.1333</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="4" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="38" priority="4" operator="lessThanOrEqual">
       <formula>13.33%</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9">
-    <cfRule type="containsText" dxfId="22" priority="9" operator="containsText" text="Candidate">
+    <cfRule type="containsText" dxfId="37" priority="9" operator="containsText" text="Candidate">
       <formula>NOT(ISERROR(SEARCH("Candidate",D9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="10" stopIfTrue="1" operator="containsText" text="Optimized">
+    <cfRule type="containsText" dxfId="36" priority="10" stopIfTrue="1" operator="containsText" text="Optimized">
       <formula>NOT(ISERROR(SEARCH("Optimized",D9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D21">
-    <cfRule type="containsText" dxfId="20" priority="1" operator="containsText" text="Optimized">
+    <cfRule type="containsText" dxfId="35" priority="1" operator="containsText" text="Optimized">
       <formula>NOT(ISERROR(SEARCH("Optimized",D21)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="19" priority="2" operator="containsText" text="Candidate">
+    <cfRule type="containsText" dxfId="34" priority="2" operator="containsText" text="Candidate">
       <formula>NOT(ISERROR(SEARCH("Candidate",D21)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="cellIs" dxfId="18" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="33" priority="7" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="32" priority="8" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21">
-    <cfRule type="cellIs" dxfId="16" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="31" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="30" priority="6" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8152,34 +8166,34 @@
     </row>
     <row r="3" spans="1:19" ht="18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>106</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="D3" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="E3" s="27">
-        <v>0.33677000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="F3" s="27">
-        <v>0.13471</v>
+        <v>0.1</v>
       </c>
       <c r="G3" s="26">
-        <v>8.7465000000000004E-4</v>
+        <v>6.4999999999999997E-4</v>
       </c>
       <c r="H3" s="26">
-        <v>1.7493000000000001E-4</v>
+        <v>1.2999999999999999E-4</v>
       </c>
       <c r="I3" s="26">
-        <v>9.6469999999999998E-4</v>
+        <v>8.0999999999999996E-4</v>
       </c>
       <c r="J3" s="26">
-        <v>2.187E-4</v>
+        <v>1.6000000000000001E-4</v>
       </c>
       <c r="K3" s="28">
         <v>0.84</v>
@@ -8195,11 +8209,11 @@
       </c>
       <c r="O3" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- WCU]]/Table4[[#This Row],[Provisioned - WCU]]</f>
-        <v>1.1029554679014462</v>
+        <v>1.2461538461538462</v>
       </c>
       <c r="P3" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- RCU]]/Table4[[#This Row],[Provisioned - RCU]]</f>
-        <v>1.2502143714628708</v>
+        <v>1.2307692307692311</v>
       </c>
       <c r="Q3" s="28">
         <f>Table4[[#This Row],[OD_IA_WRU]]/Table4[[#This Row],[OD_WRU]]</f>
@@ -8211,39 +8225,39 @@
       </c>
       <c r="S3" s="28">
         <f>Table4[[#This Row],[Standard_IA]]/Table4[[#This Row],[Standard]]</f>
-        <v>0.40000593877126822</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>104</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>96</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>105</v>
       </c>
       <c r="D4" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="E4" s="27">
-        <v>0.3135</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="F4" s="27">
-        <v>0.12540000000000001</v>
+        <v>0.112</v>
       </c>
       <c r="G4" s="26">
-        <v>8.1400000000000005E-4</v>
+        <v>7.2499999999999995E-4</v>
       </c>
       <c r="H4" s="26">
-        <v>1.628E-4</v>
+        <v>1.45E-4</v>
       </c>
       <c r="I4" s="26">
-        <v>1.018E-3</v>
+        <v>9.0600000000000001E-4</v>
       </c>
       <c r="J4" s="26">
-        <v>2.0350000000000001E-4</v>
+        <v>1.8100000000000001E-4</v>
       </c>
       <c r="K4" s="28">
         <v>0.78500000000000003</v>
@@ -8259,11 +8273,11 @@
       </c>
       <c r="O4" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- WCU]]/Table4[[#This Row],[Provisioned - WCU]]</f>
-        <v>1.2506142506142506</v>
+        <v>1.2496551724137932</v>
       </c>
       <c r="P4" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- RCU]]/Table4[[#This Row],[Provisioned - RCU]]</f>
-        <v>1.25</v>
+        <v>1.2482758620689656</v>
       </c>
       <c r="Q4" s="28">
         <f>Table4[[#This Row],[OD_IA_WRU]]/Table4[[#This Row],[OD_WRU]]</f>
@@ -8275,39 +8289,39 @@
       </c>
       <c r="S4" s="28">
         <f>Table4[[#This Row],[Standard_IA]]/Table4[[#This Row],[Standard]]</f>
-        <v>0.4</v>
+        <v>0.39999999999999997</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="D5" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="E5" s="27">
-        <v>0.28499999999999998</v>
+        <v>0.3</v>
       </c>
       <c r="F5" s="27">
-        <v>0.114</v>
+        <v>0.12</v>
       </c>
       <c r="G5" s="26">
-        <v>7.3999999999999999E-4</v>
+        <v>7.7999999999999999E-4</v>
       </c>
       <c r="H5" s="26">
-        <v>1.4799999999999999E-4</v>
+        <v>1.56E-4</v>
       </c>
       <c r="I5" s="26">
-        <v>9.3000000000000005E-4</v>
+        <v>9.7499999999999996E-4</v>
       </c>
       <c r="J5" s="26">
-        <v>1.85E-4</v>
+        <v>1.95E-4</v>
       </c>
       <c r="K5" s="28">
         <v>0.71</v>
@@ -8323,7 +8337,7 @@
       </c>
       <c r="O5" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- WCU]]/Table4[[#This Row],[Provisioned - WCU]]</f>
-        <v>1.2567567567567568</v>
+        <v>1.25</v>
       </c>
       <c r="P5" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- RCU]]/Table4[[#This Row],[Provisioned - RCU]]</f>
@@ -8344,34 +8358,34 @@
     </row>
     <row r="6" spans="1:19" ht="18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>101</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="D6" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E6" s="27">
-        <v>0.28499999999999998</v>
+        <v>0.3</v>
       </c>
       <c r="F6" s="27">
-        <v>0.114</v>
+        <v>0.12</v>
       </c>
       <c r="G6" s="26">
-        <v>7.3999999999999999E-4</v>
+        <v>7.7999999999999999E-4</v>
       </c>
       <c r="H6" s="26">
-        <v>1.4799999999999999E-4</v>
+        <v>1.56E-4</v>
       </c>
       <c r="I6" s="26">
-        <v>9.3000000000000005E-4</v>
+        <v>9.7499999999999996E-4</v>
       </c>
       <c r="J6" s="26">
-        <v>1.8550000000000001E-4</v>
+        <v>1.95E-4</v>
       </c>
       <c r="K6" s="28">
         <v>0.71</v>
@@ -8387,11 +8401,11 @@
       </c>
       <c r="O6" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- WCU]]/Table4[[#This Row],[Provisioned - WCU]]</f>
-        <v>1.2567567567567568</v>
+        <v>1.25</v>
       </c>
       <c r="P6" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- RCU]]/Table4[[#This Row],[Provisioned - RCU]]</f>
-        <v>1.2533783783783785</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" s="28">
         <f>Table4[[#This Row],[OD_IA_WRU]]/Table4[[#This Row],[OD_WRU]]</f>
@@ -8408,34 +8422,34 @@
     </row>
     <row r="7" spans="1:19" ht="18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="E7" s="27">
-        <v>0.28499999999999998</v>
+        <v>0.25</v>
       </c>
       <c r="F7" s="27">
-        <v>0.114</v>
+        <v>0.1</v>
       </c>
       <c r="G7" s="26">
-        <v>7.3999999999999999E-4</v>
+        <v>6.4999999999999997E-4</v>
       </c>
       <c r="H7" s="26">
-        <v>1.4799999999999999E-4</v>
+        <v>1.2999999999999999E-4</v>
       </c>
       <c r="I7" s="26">
-        <v>9.3000000000000005E-4</v>
+        <v>8.0999999999999996E-4</v>
       </c>
       <c r="J7" s="26">
-        <v>1.8550000000000001E-4</v>
+        <v>1.6000000000000001E-4</v>
       </c>
       <c r="K7" s="28">
         <v>0.71</v>
@@ -8451,11 +8465,11 @@
       </c>
       <c r="O7" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- WCU]]/Table4[[#This Row],[Provisioned - WCU]]</f>
-        <v>1.2567567567567568</v>
+        <v>1.2461538461538462</v>
       </c>
       <c r="P7" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- RCU]]/Table4[[#This Row],[Provisioned - RCU]]</f>
-        <v>1.2533783783783785</v>
+        <v>1.2307692307692311</v>
       </c>
       <c r="Q7" s="28">
         <f>Table4[[#This Row],[OD_IA_WRU]]/Table4[[#This Row],[OD_WRU]]</f>
@@ -8472,34 +8486,34 @@
     </row>
     <row r="8" spans="1:19" ht="18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="E8" s="27">
-        <v>0.28499999999999998</v>
+        <v>0.25</v>
       </c>
       <c r="F8" s="27">
-        <v>0.114</v>
+        <v>0.1</v>
       </c>
       <c r="G8" s="26">
-        <v>7.3999999999999999E-4</v>
+        <v>6.4999999999999997E-4</v>
       </c>
       <c r="H8" s="26">
-        <v>1.4799999999999999E-4</v>
+        <v>1.2999999999999999E-4</v>
       </c>
       <c r="I8" s="26">
-        <v>9.3000000000000005E-4</v>
+        <v>8.0999999999999996E-4</v>
       </c>
       <c r="J8" s="26">
-        <v>1.85E-4</v>
+        <v>1.6000000000000001E-4</v>
       </c>
       <c r="K8" s="28">
         <v>0.71</v>
@@ -8515,11 +8529,11 @@
       </c>
       <c r="O8" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- WCU]]/Table4[[#This Row],[Provisioned - WCU]]</f>
-        <v>1.2567567567567568</v>
+        <v>1.2461538461538462</v>
       </c>
       <c r="P8" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- RCU]]/Table4[[#This Row],[Provisioned - RCU]]</f>
-        <v>1.25</v>
+        <v>1.2307692307692311</v>
       </c>
       <c r="Q8" s="28">
         <f>Table4[[#This Row],[OD_IA_WRU]]/Table4[[#This Row],[OD_WRU]]</f>
@@ -8536,34 +8550,34 @@
     </row>
     <row r="9" spans="1:19" ht="18" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>93</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="E9" s="27">
-        <v>0.28499999999999998</v>
+        <v>0.375</v>
       </c>
       <c r="F9" s="27">
-        <v>0.114</v>
+        <v>0.15</v>
       </c>
       <c r="G9" s="26">
-        <v>7.4200000000000004E-4</v>
+        <v>9.7499999999999996E-4</v>
       </c>
       <c r="H9" s="26">
-        <v>1.484E-4</v>
+        <v>1.95E-4</v>
       </c>
       <c r="I9" s="26">
-        <v>9.2800000000000001E-4</v>
+        <v>1.219E-3</v>
       </c>
       <c r="J9" s="26">
-        <v>1.8550000000000001E-4</v>
+        <v>2.4399999999999999E-4</v>
       </c>
       <c r="K9" s="28">
         <v>0.71</v>
@@ -8579,11 +8593,11 @@
       </c>
       <c r="O9" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- WCU]]/Table4[[#This Row],[Provisioned - WCU]]</f>
-        <v>1.2506738544474394</v>
+        <v>1.2502564102564104</v>
       </c>
       <c r="P9" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- RCU]]/Table4[[#This Row],[Provisioned - RCU]]</f>
-        <v>1.25</v>
+        <v>1.2512820512820513</v>
       </c>
       <c r="Q9" s="28">
         <f>Table4[[#This Row],[OD_IA_WRU]]/Table4[[#This Row],[OD_WRU]]</f>
@@ -8595,39 +8609,39 @@
       </c>
       <c r="S9" s="28">
         <f>Table4[[#This Row],[Standard_IA]]/Table4[[#This Row],[Standard]]</f>
-        <v>0.4</v>
+        <v>0.39999999999999997</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="E10" s="27">
-        <v>0.27074999999999999</v>
+        <v>0.31130000000000002</v>
       </c>
       <c r="F10" s="27">
-        <v>0.10829999999999999</v>
+        <v>0.1245</v>
       </c>
       <c r="G10" s="26">
-        <v>7.0489999999999995E-4</v>
+        <v>8.0849999999999997E-4</v>
       </c>
       <c r="H10" s="26">
-        <v>1.4098E-4</v>
+        <v>1.617E-4</v>
       </c>
       <c r="I10" s="26">
-        <v>8.811E-4</v>
+        <v>1.0106E-3</v>
       </c>
       <c r="J10" s="26">
-        <v>1.762E-4</v>
+        <v>2.0210000000000001E-4</v>
       </c>
       <c r="K10" s="28">
         <v>0.68</v>
@@ -8643,11 +8657,11 @@
       </c>
       <c r="O10" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- WCU]]/Table4[[#This Row],[Provisioned - WCU]]</f>
-        <v>1.2499645339764507</v>
+        <v>1.2499690785405071</v>
       </c>
       <c r="P10" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- RCU]]/Table4[[#This Row],[Provisioned - RCU]]</f>
-        <v>1.2498226698822528</v>
+        <v>1.2498453927025357</v>
       </c>
       <c r="Q10" s="28">
         <f>Table4[[#This Row],[OD_IA_WRU]]/Table4[[#This Row],[OD_WRU]]</f>
@@ -8659,39 +8673,39 @@
       </c>
       <c r="S10" s="28">
         <f>Table4[[#This Row],[Standard_IA]]/Table4[[#This Row],[Standard]]</f>
-        <v>0.39999999999999997</v>
+        <v>0.39993575329264375</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="E11" s="27">
-        <v>0.28499999999999998</v>
+        <v>0.31130000000000002</v>
       </c>
       <c r="F11" s="27">
-        <v>0.114</v>
+        <v>0.12452000000000001</v>
       </c>
       <c r="G11" s="26">
-        <v>7.3999999999999999E-4</v>
+        <v>8.0849999999999997E-4</v>
       </c>
       <c r="H11" s="26">
-        <v>1.4799999999999999E-4</v>
+        <v>1.617E-4</v>
       </c>
       <c r="I11" s="26">
-        <v>9.3000000000000005E-4</v>
+        <v>1.0108999999999999E-3</v>
       </c>
       <c r="J11" s="26">
-        <v>1.8550000000000001E-4</v>
+        <v>2.0239999999999999E-4</v>
       </c>
       <c r="K11" s="28">
         <v>0.71</v>
@@ -8707,11 +8721,11 @@
       </c>
       <c r="O11" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- WCU]]/Table4[[#This Row],[Provisioned - WCU]]</f>
-        <v>1.2567567567567568</v>
+        <v>1.2503401360544217</v>
       </c>
       <c r="P11" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- RCU]]/Table4[[#This Row],[Provisioned - RCU]]</f>
-        <v>1.2533783783783785</v>
+        <v>1.2517006802721087</v>
       </c>
       <c r="Q11" s="28">
         <f>Table4[[#This Row],[OD_IA_WRU]]/Table4[[#This Row],[OD_WRU]]</f>
@@ -8723,39 +8737,39 @@
       </c>
       <c r="S11" s="28">
         <f>Table4[[#This Row],[Standard_IA]]/Table4[[#This Row],[Standard]]</f>
-        <v>0.4</v>
+        <v>0.39999999999999997</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="E12" s="27">
-        <v>0.28499999999999998</v>
+        <v>0.33960000000000001</v>
       </c>
       <c r="F12" s="27">
-        <v>0.114</v>
+        <v>0.13583999999999999</v>
       </c>
       <c r="G12" s="26">
-        <v>7.3999999999999999E-4</v>
+        <v>8.8199999999999997E-4</v>
       </c>
       <c r="H12" s="26">
-        <v>1.4799999999999999E-4</v>
+        <v>1.7640000000000001E-4</v>
       </c>
       <c r="I12" s="26">
-        <v>9.3000000000000005E-4</v>
+        <v>1.1027999999999999E-3</v>
       </c>
       <c r="J12" s="26">
-        <v>1.8550000000000001E-4</v>
+        <v>2.208E-4</v>
       </c>
       <c r="K12" s="28">
         <v>0.71</v>
@@ -8771,11 +8785,11 @@
       </c>
       <c r="O12" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- WCU]]/Table4[[#This Row],[Provisioned - WCU]]</f>
-        <v>1.2567567567567568</v>
+        <v>1.2503401360544217</v>
       </c>
       <c r="P12" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- RCU]]/Table4[[#This Row],[Provisioned - RCU]]</f>
-        <v>1.2533783783783785</v>
+        <v>1.2517006802721089</v>
       </c>
       <c r="Q12" s="28">
         <f>Table4[[#This Row],[OD_IA_WRU]]/Table4[[#This Row],[OD_WRU]]</f>
@@ -8787,39 +8801,39 @@
       </c>
       <c r="S12" s="28">
         <f>Table4[[#This Row],[Standard_IA]]/Table4[[#This Row],[Standard]]</f>
-        <v>0.4</v>
+        <v>0.39999999999999997</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="E13" s="27">
-        <v>0.28499999999999998</v>
+        <v>0.29715000000000003</v>
       </c>
       <c r="F13" s="27">
-        <v>0.114</v>
+        <v>0.11885999999999999</v>
       </c>
       <c r="G13" s="26">
-        <v>7.4200000000000004E-4</v>
+        <v>7.7200000000000001E-4</v>
       </c>
       <c r="H13" s="26">
-        <v>1.484E-4</v>
+        <v>1.5440000000000001E-4</v>
       </c>
       <c r="I13" s="26">
-        <v>9.2750000000000005E-4</v>
+        <v>9.6500000000000004E-4</v>
       </c>
       <c r="J13" s="26">
-        <v>1.8550000000000001E-4</v>
+        <v>1.93E-4</v>
       </c>
       <c r="K13" s="28">
         <v>0.71499999999999997</v>
@@ -8851,39 +8865,39 @@
       </c>
       <c r="S13" s="28">
         <f>Table4[[#This Row],[Standard_IA]]/Table4[[#This Row],[Standard]]</f>
-        <v>0.4</v>
+        <v>0.39999999999999997</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="B14" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E14" s="27">
-        <v>0.3</v>
+        <v>0.29715000000000003</v>
       </c>
       <c r="F14" s="27">
-        <v>0.12</v>
+        <v>0.11885999999999999</v>
       </c>
       <c r="G14" s="26">
-        <v>7.7999999999999999E-4</v>
+        <v>7.7200000000000001E-4</v>
       </c>
       <c r="H14" s="26">
-        <v>1.56E-4</v>
+        <v>1.5440000000000001E-4</v>
       </c>
       <c r="I14" s="26">
-        <v>9.7499999999999996E-4</v>
+        <v>9.6500000000000004E-4</v>
       </c>
       <c r="J14" s="26">
-        <v>1.95E-4</v>
+        <v>1.93E-4</v>
       </c>
       <c r="K14" s="28">
         <v>0.75</v>
@@ -8915,39 +8929,39 @@
       </c>
       <c r="S14" s="28">
         <f>Table4[[#This Row],[Standard_IA]]/Table4[[#This Row],[Standard]]</f>
-        <v>0.4</v>
+        <v>0.39999999999999997</v>
       </c>
     </row>
     <row r="15" spans="1:19" ht="18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="B15" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="D15" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E15" s="27">
-        <v>0.3</v>
+        <v>0.28299999999999997</v>
       </c>
       <c r="F15" s="27">
-        <v>0.12</v>
+        <v>0.1132</v>
       </c>
       <c r="G15" s="26">
-        <v>7.7999999999999999E-4</v>
+        <v>7.3499999999999998E-4</v>
       </c>
       <c r="H15" s="26">
-        <v>1.56E-4</v>
+        <v>1.47E-4</v>
       </c>
       <c r="I15" s="26">
-        <v>9.7499999999999996E-4</v>
+        <v>9.19E-4</v>
       </c>
       <c r="J15" s="26">
-        <v>1.95E-4</v>
+        <v>1.84E-4</v>
       </c>
       <c r="K15" s="28">
         <v>0.75</v>
@@ -8963,11 +8977,11 @@
       </c>
       <c r="O15" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- WCU]]/Table4[[#This Row],[Provisioned - WCU]]</f>
-        <v>1.25</v>
+        <v>1.2503401360544217</v>
       </c>
       <c r="P15" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- RCU]]/Table4[[#This Row],[Provisioned - RCU]]</f>
-        <v>1.25</v>
+        <v>1.2517006802721089</v>
       </c>
       <c r="Q15" s="28">
         <f>Table4[[#This Row],[OD_IA_WRU]]/Table4[[#This Row],[OD_WRU]]</f>
@@ -8984,34 +8998,34 @@
     </row>
     <row r="16" spans="1:19" ht="18" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="D16" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="E16" s="27">
-        <v>0.27500000000000002</v>
+        <v>0.28299999999999997</v>
       </c>
       <c r="F16" s="27">
-        <v>0.11</v>
+        <v>0.1132</v>
       </c>
       <c r="G16" s="26">
-        <v>7.1500000000000003E-4</v>
+        <v>7.3499999999999998E-4</v>
       </c>
       <c r="H16" s="26">
-        <v>1.4300000000000001E-4</v>
+        <v>1.47E-4</v>
       </c>
       <c r="I16" s="26">
-        <v>8.9400000000000005E-4</v>
+        <v>9.19E-4</v>
       </c>
       <c r="J16" s="26">
-        <v>1.7899999999999999E-4</v>
+        <v>1.84E-4</v>
       </c>
       <c r="K16" s="28">
         <v>0.6875</v>
@@ -9027,11 +9041,11 @@
       </c>
       <c r="O16" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- WCU]]/Table4[[#This Row],[Provisioned - WCU]]</f>
-        <v>1.2503496503496503</v>
+        <v>1.2503401360544217</v>
       </c>
       <c r="P16" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- RCU]]/Table4[[#This Row],[Provisioned - RCU]]</f>
-        <v>1.2517482517482517</v>
+        <v>1.2517006802721089</v>
       </c>
       <c r="Q16" s="28">
         <f>Table4[[#This Row],[OD_IA_WRU]]/Table4[[#This Row],[OD_WRU]]</f>
@@ -9043,39 +9057,39 @@
       </c>
       <c r="S16" s="28">
         <f>Table4[[#This Row],[Standard_IA]]/Table4[[#This Row],[Standard]]</f>
-        <v>0.39999999999999997</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="18" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="D17" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="E17" s="27">
-        <v>0.27500000000000002</v>
+        <v>0.29715000000000003</v>
       </c>
       <c r="F17" s="27">
-        <v>0.11</v>
+        <v>0.11885999999999999</v>
       </c>
       <c r="G17" s="26">
-        <v>7.1500000000000003E-4</v>
+        <v>7.7174999999999998E-4</v>
       </c>
       <c r="H17" s="26">
-        <v>1.4300000000000001E-4</v>
+        <v>1.5435000000000001E-4</v>
       </c>
       <c r="I17" s="26">
-        <v>8.9400000000000005E-4</v>
+        <v>9.6469999999999998E-4</v>
       </c>
       <c r="J17" s="26">
-        <v>1.7899999999999999E-4</v>
+        <v>1.93E-4</v>
       </c>
       <c r="K17" s="28">
         <v>0.6875</v>
@@ -9091,11 +9105,11 @@
       </c>
       <c r="O17" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- WCU]]/Table4[[#This Row],[Provisioned - WCU]]</f>
-        <v>1.2503496503496503</v>
+        <v>1.2500161969549726</v>
       </c>
       <c r="P17" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- RCU]]/Table4[[#This Row],[Provisioned - RCU]]</f>
-        <v>1.2517482517482517</v>
+        <v>1.2504049238743116</v>
       </c>
       <c r="Q17" s="28">
         <f>Table4[[#This Row],[OD_IA_WRU]]/Table4[[#This Row],[OD_WRU]]</f>
@@ -9112,34 +9126,34 @@
     </row>
     <row r="18" spans="1:19" ht="18" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D18" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="E18" s="27">
-        <v>0.30599999999999999</v>
+        <v>0.26900000000000002</v>
       </c>
       <c r="F18" s="27">
-        <v>0.12239999999999999</v>
+        <v>0.1076</v>
       </c>
       <c r="G18" s="26">
-        <v>7.9299999999999998E-4</v>
+        <v>6.9800000000000005E-4</v>
       </c>
       <c r="H18" s="26">
-        <v>1.5860000000000001E-4</v>
+        <v>1.3999999999999999E-4</v>
       </c>
       <c r="I18" s="26">
-        <v>9.9099999999999991E-4</v>
+        <v>8.7250000000000001E-4</v>
       </c>
       <c r="J18" s="26">
-        <v>1.983E-4</v>
+        <v>1.75E-4</v>
       </c>
       <c r="K18" s="28">
         <v>0.76249999999999996</v>
@@ -9155,11 +9169,11 @@
       </c>
       <c r="O18" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- WCU]]/Table4[[#This Row],[Provisioned - WCU]]</f>
-        <v>1.2496847414880201</v>
+        <v>1.25</v>
       </c>
       <c r="P18" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- RCU]]/Table4[[#This Row],[Provisioned - RCU]]</f>
-        <v>1.2503152585119797</v>
+        <v>1.25</v>
       </c>
       <c r="Q18" s="28">
         <f>Table4[[#This Row],[OD_IA_WRU]]/Table4[[#This Row],[OD_WRU]]</f>
@@ -9176,34 +9190,34 @@
     </row>
     <row r="19" spans="1:19" ht="18" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="D19" t="s">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="E19" s="27">
-        <v>0.28299999999999997</v>
+        <v>0.33660000000000001</v>
       </c>
       <c r="F19" s="27">
-        <v>0.1132</v>
+        <v>0.13464000000000001</v>
       </c>
       <c r="G19" s="26">
-        <v>7.3499999999999998E-4</v>
+        <v>8.7200000000000005E-4</v>
       </c>
       <c r="H19" s="26">
-        <v>1.47E-4</v>
+        <v>1.75E-4</v>
       </c>
       <c r="I19" s="26">
-        <v>9.19E-4</v>
+        <v>1.0901000000000001E-3</v>
       </c>
       <c r="J19" s="26">
-        <v>1.84E-4</v>
+        <v>2.1800000000000001E-4</v>
       </c>
       <c r="K19" s="28">
         <v>0.70499999999999996</v>
@@ -9219,11 +9233,11 @@
       </c>
       <c r="O19" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- WCU]]/Table4[[#This Row],[Provisioned - WCU]]</f>
-        <v>1.2503401360544217</v>
+        <v>1.2501146788990827</v>
       </c>
       <c r="P19" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- RCU]]/Table4[[#This Row],[Provisioned - RCU]]</f>
-        <v>1.2517006802721089</v>
+        <v>1.2457142857142858</v>
       </c>
       <c r="Q19" s="28">
         <f>Table4[[#This Row],[OD_IA_WRU]]/Table4[[#This Row],[OD_WRU]]</f>
@@ -9240,34 +9254,34 @@
     </row>
     <row r="20" spans="1:19" ht="18" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="C20" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="E20" s="27">
-        <v>0.29715000000000003</v>
+        <v>0.30599999999999999</v>
       </c>
       <c r="F20" s="27">
-        <v>0.11885999999999999</v>
+        <v>0.12239999999999999</v>
       </c>
       <c r="G20" s="26">
-        <v>7.7200000000000001E-4</v>
+        <v>7.9299999999999998E-4</v>
       </c>
       <c r="H20" s="26">
-        <v>1.5440000000000001E-4</v>
+        <v>1.5860000000000001E-4</v>
       </c>
       <c r="I20" s="26">
-        <v>9.6500000000000004E-4</v>
+        <v>9.9099999999999991E-4</v>
       </c>
       <c r="J20" s="26">
-        <v>1.93E-4</v>
+        <v>1.983E-4</v>
       </c>
       <c r="K20" s="28">
         <v>0.74229999999999996</v>
@@ -9283,11 +9297,11 @@
       </c>
       <c r="O20" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- WCU]]/Table4[[#This Row],[Provisioned - WCU]]</f>
-        <v>1.25</v>
+        <v>1.2496847414880201</v>
       </c>
       <c r="P20" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- RCU]]/Table4[[#This Row],[Provisioned - RCU]]</f>
-        <v>1.25</v>
+        <v>1.2503152585119797</v>
       </c>
       <c r="Q20" s="28">
         <f>Table4[[#This Row],[OD_IA_WRU]]/Table4[[#This Row],[OD_WRU]]</f>
@@ -9304,34 +9318,34 @@
     </row>
     <row r="21" spans="1:19" ht="18" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="B21" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="C21" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="D21" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="E21" s="27">
-        <v>0.29715000000000003</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="F21" s="27">
-        <v>0.11885999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="G21" s="26">
-        <v>7.7174999999999998E-4</v>
+        <v>7.1500000000000003E-4</v>
       </c>
       <c r="H21" s="26">
-        <v>1.5435000000000001E-4</v>
+        <v>1.4300000000000001E-4</v>
       </c>
       <c r="I21" s="26">
-        <v>9.6469999999999998E-4</v>
+        <v>8.9400000000000005E-4</v>
       </c>
       <c r="J21" s="26">
-        <v>1.93E-4</v>
+        <v>1.7899999999999999E-4</v>
       </c>
       <c r="K21" s="28">
         <v>0.74</v>
@@ -9347,11 +9361,11 @@
       </c>
       <c r="O21" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- WCU]]/Table4[[#This Row],[Provisioned - WCU]]</f>
-        <v>1.2500161969549726</v>
+        <v>1.2503496503496503</v>
       </c>
       <c r="P21" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- RCU]]/Table4[[#This Row],[Provisioned - RCU]]</f>
-        <v>1.2504049238743116</v>
+        <v>1.2517482517482517</v>
       </c>
       <c r="Q21" s="28">
         <f>Table4[[#This Row],[OD_IA_WRU]]/Table4[[#This Row],[OD_WRU]]</f>
@@ -9368,34 +9382,34 @@
     </row>
     <row r="22" spans="1:19" ht="18" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="C22" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="D22" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E22" s="27">
-        <v>0.29715000000000003</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="F22" s="27">
-        <v>0.11885999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="G22" s="26">
-        <v>7.7200000000000001E-4</v>
+        <v>7.1500000000000003E-4</v>
       </c>
       <c r="H22" s="26">
-        <v>1.5440000000000001E-4</v>
+        <v>1.4300000000000001E-4</v>
       </c>
       <c r="I22" s="26">
-        <v>9.6500000000000004E-4</v>
+        <v>8.9400000000000005E-4</v>
       </c>
       <c r="J22" s="26">
-        <v>1.93E-4</v>
+        <v>1.7899999999999999E-4</v>
       </c>
       <c r="K22" s="28">
         <v>0.74229999999999996</v>
@@ -9411,11 +9425,11 @@
       </c>
       <c r="O22" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- WCU]]/Table4[[#This Row],[Provisioned - WCU]]</f>
-        <v>1.25</v>
+        <v>1.2503496503496503</v>
       </c>
       <c r="P22" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- RCU]]/Table4[[#This Row],[Provisioned - RCU]]</f>
-        <v>1.25</v>
+        <v>1.2517482517482517</v>
       </c>
       <c r="Q22" s="28">
         <f>Table4[[#This Row],[OD_IA_WRU]]/Table4[[#This Row],[OD_WRU]]</f>
@@ -9432,34 +9446,34 @@
     </row>
     <row r="23" spans="1:19" ht="18" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="B23" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="D23" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E23" s="27">
-        <v>0.28299999999999997</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="F23" s="27">
-        <v>0.1132</v>
+        <v>0.114</v>
       </c>
       <c r="G23" s="26">
-        <v>7.3499999999999998E-4</v>
+        <v>7.3999999999999999E-4</v>
       </c>
       <c r="H23" s="26">
-        <v>1.47E-4</v>
+        <v>1.4799999999999999E-4</v>
       </c>
       <c r="I23" s="26">
-        <v>9.19E-4</v>
+        <v>9.3000000000000005E-4</v>
       </c>
       <c r="J23" s="26">
-        <v>1.84E-4</v>
+        <v>1.8550000000000001E-4</v>
       </c>
       <c r="K23" s="28">
         <v>0.70499999999999996</v>
@@ -9475,11 +9489,11 @@
       </c>
       <c r="O23" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- WCU]]/Table4[[#This Row],[Provisioned - WCU]]</f>
-        <v>1.2503401360544217</v>
+        <v>1.2567567567567568</v>
       </c>
       <c r="P23" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- RCU]]/Table4[[#This Row],[Provisioned - RCU]]</f>
-        <v>1.2517006802721089</v>
+        <v>1.2533783783783785</v>
       </c>
       <c r="Q23" s="28">
         <f>Table4[[#This Row],[OD_IA_WRU]]/Table4[[#This Row],[OD_WRU]]</f>
@@ -9496,34 +9510,34 @@
     </row>
     <row r="24" spans="1:19" ht="18" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="C24" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="D24" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E24" s="27">
-        <v>0.26900000000000002</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="F24" s="27">
-        <v>0.1076</v>
+        <v>0.114</v>
       </c>
       <c r="G24" s="26">
-        <v>6.9800000000000005E-4</v>
+        <v>7.3999999999999999E-4</v>
       </c>
       <c r="H24" s="26">
-        <v>1.3999999999999999E-4</v>
+        <v>1.4799999999999999E-4</v>
       </c>
       <c r="I24" s="26">
-        <v>8.7250000000000001E-4</v>
+        <v>9.3000000000000005E-4</v>
       </c>
       <c r="J24" s="26">
-        <v>1.75E-4</v>
+        <v>1.8550000000000001E-4</v>
       </c>
       <c r="K24" s="28">
         <v>0.67</v>
@@ -9539,11 +9553,11 @@
       </c>
       <c r="O24" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- WCU]]/Table4[[#This Row],[Provisioned - WCU]]</f>
-        <v>1.25</v>
+        <v>1.2567567567567568</v>
       </c>
       <c r="P24" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- RCU]]/Table4[[#This Row],[Provisioned - RCU]]</f>
-        <v>1.25</v>
+        <v>1.2533783783783785</v>
       </c>
       <c r="Q24" s="28">
         <f>Table4[[#This Row],[OD_IA_WRU]]/Table4[[#This Row],[OD_WRU]]</f>
@@ -9555,39 +9569,39 @@
       </c>
       <c r="S24" s="28">
         <f>Table4[[#This Row],[Standard_IA]]/Table4[[#This Row],[Standard]]</f>
-        <v>0.39999999999999997</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="18" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="B25" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C25" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="D25" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="E25" s="27">
-        <v>0.33660000000000001</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="F25" s="27">
-        <v>0.13464000000000001</v>
+        <v>0.114</v>
       </c>
       <c r="G25" s="26">
-        <v>8.7200000000000005E-4</v>
+        <v>7.3999999999999999E-4</v>
       </c>
       <c r="H25" s="26">
-        <v>1.75E-4</v>
+        <v>1.4799999999999999E-4</v>
       </c>
       <c r="I25" s="26">
-        <v>1.0901000000000001E-3</v>
+        <v>9.3000000000000005E-4</v>
       </c>
       <c r="J25" s="26">
-        <v>2.1800000000000001E-4</v>
+        <v>1.8550000000000001E-4</v>
       </c>
       <c r="K25" s="28">
         <v>0.83499999999999996</v>
@@ -9603,11 +9617,11 @@
       </c>
       <c r="O25" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- WCU]]/Table4[[#This Row],[Provisioned - WCU]]</f>
-        <v>1.2501146788990827</v>
+        <v>1.2567567567567568</v>
       </c>
       <c r="P25" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- RCU]]/Table4[[#This Row],[Provisioned - RCU]]</f>
-        <v>1.2457142857142858</v>
+        <v>1.2533783783783785</v>
       </c>
       <c r="Q25" s="28">
         <f>Table4[[#This Row],[OD_IA_WRU]]/Table4[[#This Row],[OD_WRU]]</f>
@@ -9624,34 +9638,34 @@
     </row>
     <row r="26" spans="1:19" ht="18" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="D26" t="s">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="E26" s="27">
-        <v>0.33960000000000001</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="F26" s="27">
-        <v>0.13583999999999999</v>
+        <v>0.114</v>
       </c>
       <c r="G26" s="26">
-        <v>8.8199999999999997E-4</v>
+        <v>7.3999999999999999E-4</v>
       </c>
       <c r="H26" s="26">
-        <v>1.7640000000000001E-4</v>
+        <v>1.4799999999999999E-4</v>
       </c>
       <c r="I26" s="26">
-        <v>1.1027999999999999E-3</v>
+        <v>9.3000000000000005E-4</v>
       </c>
       <c r="J26" s="26">
-        <v>2.208E-4</v>
+        <v>1.8550000000000001E-4</v>
       </c>
       <c r="K26" s="28">
         <v>0.85</v>
@@ -9667,11 +9681,11 @@
       </c>
       <c r="O26" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- WCU]]/Table4[[#This Row],[Provisioned - WCU]]</f>
-        <v>1.2503401360544217</v>
+        <v>1.2567567567567568</v>
       </c>
       <c r="P26" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- RCU]]/Table4[[#This Row],[Provisioned - RCU]]</f>
-        <v>1.2517006802721089</v>
+        <v>1.2533783783783785</v>
       </c>
       <c r="Q26" s="28">
         <f>Table4[[#This Row],[OD_IA_WRU]]/Table4[[#This Row],[OD_WRU]]</f>
@@ -9683,39 +9697,39 @@
       </c>
       <c r="S26" s="28">
         <f>Table4[[#This Row],[Standard_IA]]/Table4[[#This Row],[Standard]]</f>
-        <v>0.39999999999999997</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="27" spans="1:19" ht="18" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="D27" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="E27" s="27">
-        <v>0.31130000000000002</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="F27" s="27">
-        <v>0.1245</v>
+        <v>0.114</v>
       </c>
       <c r="G27" s="26">
-        <v>8.0849999999999997E-4</v>
+        <v>7.3999999999999999E-4</v>
       </c>
       <c r="H27" s="26">
-        <v>1.617E-4</v>
+        <v>1.4799999999999999E-4</v>
       </c>
       <c r="I27" s="26">
-        <v>1.0106E-3</v>
+        <v>9.3000000000000005E-4</v>
       </c>
       <c r="J27" s="26">
-        <v>2.0210000000000001E-4</v>
+        <v>1.85E-4</v>
       </c>
       <c r="K27" s="28">
         <v>0.77500000000000002</v>
@@ -9731,11 +9745,11 @@
       </c>
       <c r="O27" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- WCU]]/Table4[[#This Row],[Provisioned - WCU]]</f>
-        <v>1.2499690785405071</v>
+        <v>1.2567567567567568</v>
       </c>
       <c r="P27" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- RCU]]/Table4[[#This Row],[Provisioned - RCU]]</f>
-        <v>1.2498453927025357</v>
+        <v>1.25</v>
       </c>
       <c r="Q27" s="28">
         <f>Table4[[#This Row],[OD_IA_WRU]]/Table4[[#This Row],[OD_WRU]]</f>
@@ -9747,39 +9761,39 @@
       </c>
       <c r="S27" s="28">
         <f>Table4[[#This Row],[Standard_IA]]/Table4[[#This Row],[Standard]]</f>
-        <v>0.39993575329264375</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="28" spans="1:19" ht="18" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="C28" t="s">
-        <v>90</v>
+        <v>41</v>
       </c>
       <c r="D28" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="E28" s="27">
-        <v>0.31130000000000002</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="F28" s="27">
-        <v>0.12452000000000001</v>
+        <v>0.114</v>
       </c>
       <c r="G28" s="26">
-        <v>8.0849999999999997E-4</v>
+        <v>7.3999999999999999E-4</v>
       </c>
       <c r="H28" s="26">
-        <v>1.617E-4</v>
+        <v>1.4799999999999999E-4</v>
       </c>
       <c r="I28" s="26">
-        <v>1.0108999999999999E-3</v>
+        <v>9.3000000000000005E-4</v>
       </c>
       <c r="J28" s="26">
-        <v>2.0239999999999999E-4</v>
+        <v>1.85E-4</v>
       </c>
       <c r="K28" s="28">
         <v>0.77549999999999997</v>
@@ -9795,11 +9809,11 @@
       </c>
       <c r="O28" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- WCU]]/Table4[[#This Row],[Provisioned - WCU]]</f>
-        <v>1.2503401360544217</v>
+        <v>1.2567567567567568</v>
       </c>
       <c r="P28" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- RCU]]/Table4[[#This Row],[Provisioned - RCU]]</f>
-        <v>1.2517006802721087</v>
+        <v>1.25</v>
       </c>
       <c r="Q28" s="28">
         <f>Table4[[#This Row],[OD_IA_WRU]]/Table4[[#This Row],[OD_WRU]]</f>
@@ -9811,39 +9825,39 @@
       </c>
       <c r="S28" s="28">
         <f>Table4[[#This Row],[Standard_IA]]/Table4[[#This Row],[Standard]]</f>
-        <v>0.39999999999999997</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="29" spans="1:19" ht="18" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>93</v>
+        <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="C29" t="s">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="D29" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="E29" s="27">
-        <v>0.375</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="F29" s="27">
-        <v>0.15</v>
+        <v>0.114</v>
       </c>
       <c r="G29" s="26">
-        <v>9.7499999999999996E-4</v>
+        <v>7.4200000000000004E-4</v>
       </c>
       <c r="H29" s="26">
-        <v>1.95E-4</v>
+        <v>1.484E-4</v>
       </c>
       <c r="I29" s="26">
-        <v>1.219E-3</v>
+        <v>9.2800000000000001E-4</v>
       </c>
       <c r="J29" s="26">
-        <v>2.4399999999999999E-4</v>
+        <v>1.8550000000000001E-4</v>
       </c>
       <c r="K29" s="28">
         <v>0.9375</v>
@@ -9859,11 +9873,11 @@
       </c>
       <c r="O29" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- WCU]]/Table4[[#This Row],[Provisioned - WCU]]</f>
-        <v>1.2502564102564104</v>
+        <v>1.2506738544474394</v>
       </c>
       <c r="P29" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- RCU]]/Table4[[#This Row],[Provisioned - RCU]]</f>
-        <v>1.2512820512820513</v>
+        <v>1.25</v>
       </c>
       <c r="Q29" s="28">
         <f>Table4[[#This Row],[OD_IA_WRU]]/Table4[[#This Row],[OD_WRU]]</f>
@@ -9875,39 +9889,39 @@
       </c>
       <c r="S29" s="28">
         <f>Table4[[#This Row],[Standard_IA]]/Table4[[#This Row],[Standard]]</f>
-        <v>0.39999999999999997</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="30" spans="1:19" ht="18" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>37</v>
       </c>
       <c r="C30" t="s">
-        <v>97</v>
+        <v>38</v>
       </c>
       <c r="D30" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="E30" s="27">
-        <v>0.25</v>
+        <v>0.27074999999999999</v>
       </c>
       <c r="F30" s="27">
-        <v>0.1</v>
+        <v>0.10829999999999999</v>
       </c>
       <c r="G30" s="26">
-        <v>6.4999999999999997E-4</v>
+        <v>7.0489999999999995E-4</v>
       </c>
       <c r="H30" s="26">
-        <v>1.2999999999999999E-4</v>
+        <v>1.4098E-4</v>
       </c>
       <c r="I30" s="26">
-        <v>8.0999999999999996E-4</v>
+        <v>8.811E-4</v>
       </c>
       <c r="J30" s="26">
-        <v>1.6000000000000001E-4</v>
+        <v>1.762E-4</v>
       </c>
       <c r="K30" s="28">
         <v>0.625</v>
@@ -9923,11 +9937,11 @@
       </c>
       <c r="O30" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- WCU]]/Table4[[#This Row],[Provisioned - WCU]]</f>
-        <v>1.2461538461538462</v>
+        <v>1.2499645339764507</v>
       </c>
       <c r="P30" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- RCU]]/Table4[[#This Row],[Provisioned - RCU]]</f>
-        <v>1.2307692307692311</v>
+        <v>1.2498226698822528</v>
       </c>
       <c r="Q30" s="28">
         <f>Table4[[#This Row],[OD_IA_WRU]]/Table4[[#This Row],[OD_WRU]]</f>
@@ -9939,39 +9953,39 @@
       </c>
       <c r="S30" s="28">
         <f>Table4[[#This Row],[Standard_IA]]/Table4[[#This Row],[Standard]]</f>
-        <v>0.4</v>
+        <v>0.39999999999999997</v>
       </c>
     </row>
     <row r="31" spans="1:19" ht="18" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="C31" t="s">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="D31" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="E31" s="27">
-        <v>0.25</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="F31" s="27">
-        <v>0.1</v>
+        <v>0.114</v>
       </c>
       <c r="G31" s="26">
-        <v>6.4999999999999997E-4</v>
+        <v>7.4200000000000004E-4</v>
       </c>
       <c r="H31" s="26">
-        <v>1.2999999999999999E-4</v>
+        <v>1.484E-4</v>
       </c>
       <c r="I31" s="26">
-        <v>8.0999999999999996E-4</v>
+        <v>9.2750000000000005E-4</v>
       </c>
       <c r="J31" s="26">
-        <v>1.6000000000000001E-4</v>
+        <v>1.8550000000000001E-4</v>
       </c>
       <c r="K31" s="28">
         <v>0.625</v>
@@ -9987,11 +10001,11 @@
       </c>
       <c r="O31" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- WCU]]/Table4[[#This Row],[Provisioned - WCU]]</f>
-        <v>1.2461538461538462</v>
+        <v>1.25</v>
       </c>
       <c r="P31" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- RCU]]/Table4[[#This Row],[Provisioned - RCU]]</f>
-        <v>1.2307692307692311</v>
+        <v>1.25</v>
       </c>
       <c r="Q31" s="28">
         <f>Table4[[#This Row],[OD_IA_WRU]]/Table4[[#This Row],[OD_WRU]]</f>
@@ -10008,34 +10022,34 @@
     </row>
     <row r="32" spans="1:19" ht="18" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>96</v>
+        <v>31</v>
       </c>
       <c r="C32" t="s">
-        <v>105</v>
+        <v>32</v>
       </c>
       <c r="D32" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="E32" s="27">
-        <v>0.28000000000000003</v>
+        <v>0.3135</v>
       </c>
       <c r="F32" s="27">
-        <v>0.112</v>
+        <v>0.12540000000000001</v>
       </c>
       <c r="G32" s="26">
-        <v>7.2499999999999995E-4</v>
+        <v>8.1400000000000005E-4</v>
       </c>
       <c r="H32" s="26">
-        <v>1.45E-4</v>
+        <v>1.628E-4</v>
       </c>
       <c r="I32" s="26">
-        <v>9.0600000000000001E-4</v>
+        <v>1.018E-3</v>
       </c>
       <c r="J32" s="26">
-        <v>1.8100000000000001E-4</v>
+        <v>2.0350000000000001E-4</v>
       </c>
       <c r="K32" s="28">
         <v>0.69499999999999995</v>
@@ -10051,11 +10065,11 @@
       </c>
       <c r="O32" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- WCU]]/Table4[[#This Row],[Provisioned - WCU]]</f>
-        <v>1.2496551724137932</v>
+        <v>1.2506142506142506</v>
       </c>
       <c r="P32" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- RCU]]/Table4[[#This Row],[Provisioned - RCU]]</f>
-        <v>1.2482758620689656</v>
+        <v>1.25</v>
       </c>
       <c r="Q32" s="28">
         <f>Table4[[#This Row],[OD_IA_WRU]]/Table4[[#This Row],[OD_WRU]]</f>
@@ -10067,39 +10081,39 @@
       </c>
       <c r="S32" s="28">
         <f>Table4[[#This Row],[Standard_IA]]/Table4[[#This Row],[Standard]]</f>
-        <v>0.39999999999999997</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="33" spans="1:19" ht="18" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="C33" t="s">
-        <v>103</v>
+        <v>29</v>
       </c>
       <c r="D33" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="E33" s="27">
-        <v>0.25</v>
+        <v>0.33677000000000001</v>
       </c>
       <c r="F33" s="27">
-        <v>0.1</v>
+        <v>0.13471</v>
       </c>
       <c r="G33" s="26">
-        <v>6.4999999999999997E-4</v>
+        <v>8.7465000000000004E-4</v>
       </c>
       <c r="H33" s="26">
-        <v>1.2999999999999999E-4</v>
+        <v>1.7493000000000001E-4</v>
       </c>
       <c r="I33" s="26">
-        <v>8.0999999999999996E-4</v>
+        <v>9.6469999999999998E-4</v>
       </c>
       <c r="J33" s="26">
-        <v>1.6000000000000001E-4</v>
+        <v>2.187E-4</v>
       </c>
       <c r="K33" s="28">
         <v>0.625</v>
@@ -10115,11 +10129,11 @@
       </c>
       <c r="O33" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- WCU]]/Table4[[#This Row],[Provisioned - WCU]]</f>
-        <v>1.2461538461538462</v>
+        <v>1.1029554679014462</v>
       </c>
       <c r="P33" s="28">
         <f>Table4[[#This Row],[Provisioned_IA- RCU]]/Table4[[#This Row],[Provisioned - RCU]]</f>
-        <v>1.2307692307692311</v>
+        <v>1.2502143714628708</v>
       </c>
       <c r="Q33" s="28">
         <f>Table4[[#This Row],[OD_IA_WRU]]/Table4[[#This Row],[OD_WRU]]</f>
@@ -10131,7 +10145,7 @@
       </c>
       <c r="S33" s="28">
         <f>Table4[[#This Row],[Standard_IA]]/Table4[[#This Row],[Standard]]</f>
-        <v>0.4</v>
+        <v>0.40000593877126822</v>
       </c>
     </row>
     <row r="34" spans="1:19" ht="18" x14ac:dyDescent="0.2">
